--- a/data/trans_orig/IP19C07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59794</t>
+          <t>60508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>69839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>63381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74183</t>
+          <t>74656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127455</t>
+          <t>127710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141049</t>
+          <t>141438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96180</t>
+          <t>95555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105062</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95856</t>
+          <t>95794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105680</t>
+          <t>105300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>195922</t>
+          <t>194353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208300</t>
+          <t>208521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57472</t>
+          <t>57087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65549</t>
+          <t>65512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68007</t>
+          <t>68017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75353</t>
+          <t>75235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128294</t>
+          <t>127904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139246</t>
+          <t>139553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>23929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>18025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33254</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71880</t>
+          <t>72060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84721</t>
+          <t>84407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76643</t>
+          <t>76343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85914</t>
+          <t>85860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152778</t>
+          <t>152746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169181</t>
+          <t>168007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94353</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297214</t>
+          <t>297809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>317682</t>
+          <t>316795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>315738</t>
+          <t>315423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>334592</t>
+          <t>333558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>618308</t>
+          <t>618565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>646219</t>
+          <t>646042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>60622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70112</t>
+          <t>70307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>61489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71327</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127138</t>
+          <t>126389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139691</t>
+          <t>139718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17984</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94615</t>
+          <t>94380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105028</t>
+          <t>105165</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99853</t>
+          <t>99012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109344</t>
+          <t>109193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197751</t>
+          <t>197671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211830</t>
+          <t>212467</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63707</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71533</t>
+          <t>71178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67593</t>
+          <t>68175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75987</t>
+          <t>76072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135012</t>
+          <t>134514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145640</t>
+          <t>145435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18135</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27755</t>
+          <t>28201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>79344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88795</t>
+          <t>88684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78166</t>
+          <t>78284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89237</t>
+          <t>89063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161522</t>
+          <t>161076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175927</t>
+          <t>175953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47275</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58006</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>84678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>310733</t>
+          <t>310867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>328970</t>
+          <t>328874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>318727</t>
+          <t>319264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>337950</t>
+          <t>338256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>635712</t>
+          <t>636051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>662723</t>
+          <t>662412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58958</t>
+          <t>59720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68003</t>
+          <t>67892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64944</t>
+          <t>64509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73442</t>
+          <t>73455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128701</t>
+          <t>128800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139989</t>
+          <t>140239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91361</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101733</t>
+          <t>101830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101339</t>
+          <t>101285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107300</t>
+          <t>107292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196098</t>
+          <t>195464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207853</t>
+          <t>208027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68388</t>
+          <t>68626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74376</t>
+          <t>74423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68128</t>
+          <t>67741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75080</t>
+          <t>74890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139643</t>
+          <t>139870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148593</t>
+          <t>148333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92886</t>
+          <t>92539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103586</t>
+          <t>103575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92840</t>
+          <t>92804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102453</t>
+          <t>102639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190219</t>
+          <t>189109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203663</t>
+          <t>204538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323424</t>
+          <t>323401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342023</t>
+          <t>341848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338732</t>
+          <t>339054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>353151</t>
+          <t>353520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>668499</t>
+          <t>668272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>691661</t>
+          <t>690667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58983</t>
+          <t>58560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67775</t>
+          <t>67646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79831</t>
+          <t>79984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84734</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141398</t>
+          <t>141479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151360</t>
+          <t>151644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24131</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101851</t>
+          <t>101737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111272</t>
+          <t>111130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150416</t>
+          <t>150753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162572</t>
+          <t>162256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>257225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>271447</t>
+          <t>271885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91175</t>
+          <t>90744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101298</t>
+          <t>101355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103277</t>
+          <t>104609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115013</t>
+          <t>115216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198111</t>
+          <t>198828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214093</t>
+          <t>213758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84720</t>
+          <t>85862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96268</t>
+          <t>96537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99282</t>
+          <t>98854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108324</t>
+          <t>108203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189206</t>
+          <t>188897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202792</t>
+          <t>203040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41294</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38966</t>
+          <t>38241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>45816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71610</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350339</t>
+          <t>350576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368447</t>
+          <t>369561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>445478</t>
+          <t>446203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>465045</t>
+          <t>464469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>804466</t>
+          <t>804047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830394</t>
+          <t>830260</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12637</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19043</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10115</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5834</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15165</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15020</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12637</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7532</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18807</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69551</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63145</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74104</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>65558</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60508</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69839</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69777</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>69551</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63381</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74656</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127710</t>
+          <t>126965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141438</t>
+          <t>141717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10345</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16382</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8839</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5050</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14506</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5069</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14054</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,03%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10345</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6331</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15837</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>13578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>27659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>101286</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>95249</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>105220</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101222</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95555</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105011</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>96007</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>104992</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,97%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>101286</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>95794</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>105300</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194353</t>
+          <t>194033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208521</t>
+          <t>208114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2537</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6980</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3696</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3703</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11528</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9852</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72504</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67922</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75332</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>62228</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57087</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57680</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>65505</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72504</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68017</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75235</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127904</t>
+          <t>128844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139553</t>
+          <t>139443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7881</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12904</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>16964</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11582</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23929</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11430</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24714</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7881</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13700</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>33887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82162</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77139</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86051</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>79025</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72060</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>84407</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>71275</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>84559</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82162</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>76343</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>85860</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152746</t>
+          <t>152145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168007</t>
+          <t>168046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27746</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46699</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>42898</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34135</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>53121</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32872</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>52969</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28173</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>46308</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>65315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94096</t>
+          <t>93057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>325504</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>315032</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>333985</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>308032</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>297809</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>316795</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>297961</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>318058</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>325504</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>315423</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>333558</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>618565</t>
+          <t>619604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>646042</t>
+          <t>647346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7468</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12997</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8226</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4347</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14032</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4481</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13489</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7468</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4155</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13753</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67774</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62245</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71554</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66428</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60622</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>70307</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>61165</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70173</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67774</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61489</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71087</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,08%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126389</t>
+          <t>126805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139718</t>
+          <t>139806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>74654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>74654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>74654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9795</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16186</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11924</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7434</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18219</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7713</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17718</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9795</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5513</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15694</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104911</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98520</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109092</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100675</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>94380</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105165</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>94881</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>104886</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>104911</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>99012</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>109193</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197671</t>
+          <t>196469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212467</t>
+          <t>212261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11822</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6304</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3319</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10908</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11434</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7049</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3681</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11578</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72704</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67931</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75817</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68193</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63589</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>71178</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63063</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>71269</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,54%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72704</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68175</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76072</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134514</t>
+          <t>134689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145435</t>
+          <t>145570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11841</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6975</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17614</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7884</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4293</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13633</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13837</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11841</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7238</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18017</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84460</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78687</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>89326</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>85093</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>79344</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>88684</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>79140</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>88774</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>84460</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78284</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>89063</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161076</t>
+          <t>161634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175953</t>
+          <t>176185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27652</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46512</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>34337</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25853</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43860</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44516</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36153</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27746</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>46738</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84678</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>329849</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>319490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>338350</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>455</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>320390</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>310867</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>328874</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>310211</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>328357</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>329849</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>319264</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>338256</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>636051</t>
+          <t>635121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>662412</t>
+          <t>662378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>505</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>354727</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>354727</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>354727</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2335</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10485</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5981</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11121</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10809</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5335</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2342</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11288</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -4735,67 +4735,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>70462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65312</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>64860</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59720</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67892</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>60032</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68176</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70462</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64509</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73455</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128800</t>
+          <t>128718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140239</t>
+          <t>140157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7226</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10685</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6131</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17727</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6592</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17938</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7307</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>105291</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>101366</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>107303</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>97276</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90234</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101830</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>90023</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>101369</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>105291</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>101285</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>107292</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>195464</t>
+          <t>195826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208027</t>
+          <t>207608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107961</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107961</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107961</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9249</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3088</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6962</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6734</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4490</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9122</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72373</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67614</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74843</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72500</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>68626</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74423</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68854</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74404</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72373</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67741</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74890</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>139378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148333</t>
+          <t>148320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13208</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9938</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16468</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5539</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16523</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4118</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13953</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98988</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>93549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>102683</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>99069</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>92539</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>103575</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>92484</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>103468</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98988</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>92804</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102639</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189109</t>
+          <t>190130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204538</t>
+          <t>204465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15014</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29636</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>39995</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21653</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>40170</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14488</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>28954</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>40567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>63057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>347113</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>338372</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>352994</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>487</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>333704</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>323401</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>341848</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>323226</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>341743</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>347113</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>339054</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>353520</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>668272</t>
+          <t>668348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>690667</t>
+          <t>690838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>363396</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>363396</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>363396</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5040</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5272</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11206</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2359</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12123</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5265</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79644</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76417</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80933</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>64494</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58560</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67646</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>68659</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62155</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71919</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83379</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79984</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84743</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>147872</t>
+          <t>148303</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141479</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151644</t>
+          <t>151952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9444</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4994</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17315</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5981</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11996</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>152886</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145015</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>157336</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>107752</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101737</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>111130</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>157998</t>
+          <t>110630</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150753</t>
+          <t>104137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162256</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>263516</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>257225</t>
+          <t>255209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>271885</t>
+          <t>269964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9735</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4899</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16879</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10076</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16211</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>102363</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95219</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>107199</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>96879</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90744</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>101355</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>110500</t>
+          <t>92119</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104609</t>
+          <t>85165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115216</t>
+          <t>96833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>207379</t>
+          <t>194482</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198828</t>
+          <t>185979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>213758</t>
+          <t>201000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12912</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9028</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4642</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15317</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98288</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>92297</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>101942</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>92151</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>85862</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96537</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>104687</t>
+          <t>93401</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98854</t>
+          <t>86767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108203</t>
+          <t>97405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>196838</t>
+          <t>191689</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188897</t>
+          <t>183213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203040</t>
+          <t>197474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27914</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19800</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>38307</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22072</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41057</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38241</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59383</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>45499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72029</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>433181</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>422788</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>441295</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>514</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>361275</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>350576</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>369561</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>456564</t>
+          <t>364809</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>446203</t>
+          <t>353368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>464469</t>
+          <t>373431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>817838</t>
+          <t>797989</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>804047</t>
+          <t>784312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830260</t>
+          <t>811873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
